--- a/output/yearly_benthic_cover_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_92_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.33190379240936</v>
+        <v>45.41956405321881</v>
       </c>
       <c r="M2" t="n">
-        <v>99.83180937937868</v>
+        <v>99.380181828204</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01060406265539</v>
+        <v>88.0551754084282</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8877137872205</v>
+        <v>45.9169200996526</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228718834649717</v>
+        <v>2.228810999069803</v>
       </c>
       <c r="E3" t="n">
-        <v>5.682161667484571</v>
+        <v>5.701245838243782</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429062782165724</v>
+        <v>0.7429369996899342</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95905155156323</v>
+        <v>33.9687297302944</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17368879796233</v>
+        <v>34.17510198573697</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5809126939254</v>
+        <v>6.594993607331213</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643164238853577</v>
+        <v>4.643356248062089</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98939593734461</v>
+        <v>11.94482459157181</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88666800848537</v>
+        <v>48.90153739558928</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637777330505</v>
+        <v>106.7632820868137</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10237530462874</v>
+        <v>87.26130107438176</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61862522582153</v>
+        <v>42.76382056760305</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184959810341078</v>
+        <v>2.191180870402089</v>
       </c>
       <c r="E4" t="n">
-        <v>6.486535136131894</v>
+        <v>6.522887206790818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444687064458526</v>
+        <v>0.7444999849680809</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29229406773879</v>
+        <v>33.39521870986096</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24556049650922</v>
+        <v>34.24699930853172</v>
       </c>
       <c r="I4" t="n">
-        <v>5.495627672175328</v>
+        <v>5.507390087777588</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652929415286579</v>
+        <v>4.653124906050506</v>
       </c>
       <c r="K4" t="n">
-        <v>12.89762469537126</v>
+        <v>12.73869892561823</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30094694842041</v>
+        <v>44.31428623990841</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81719686961321</v>
+        <v>99.8168057331297</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.9837398448292</v>
+        <v>86.29079101357235</v>
       </c>
       <c r="C5" t="n">
-        <v>42.35290388199353</v>
+        <v>42.64819200118164</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130497490827885</v>
+        <v>2.144481727997771</v>
       </c>
       <c r="E5" t="n">
-        <v>7.089490896402586</v>
+        <v>7.150143163686387</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457927938459707</v>
+        <v>0.7458222369162092</v>
       </c>
       <c r="G5" t="n">
-        <v>32.46245017392303</v>
+        <v>32.68348920582009</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30646851691466</v>
+        <v>34.30782289814562</v>
       </c>
       <c r="I5" t="n">
-        <v>4.587835011377752</v>
+        <v>4.597642800279955</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661204961537317</v>
+        <v>4.661388980726308</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0162601551708</v>
+        <v>13.70920898642766</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47817963860857</v>
+        <v>43.48961595439688</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8473436757729</v>
+        <v>99.84701694200618</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.71201533979463</v>
+        <v>85.08849040057324</v>
       </c>
       <c r="C6" t="n">
-        <v>41.79370615710071</v>
+        <v>42.16019722146022</v>
       </c>
       <c r="D6" t="n">
-        <v>2.068608347160985</v>
+        <v>2.086192588191413</v>
       </c>
       <c r="E6" t="n">
-        <v>7.521706550992564</v>
+        <v>7.595316562622791</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469164470624536</v>
+        <v>0.7469433503923684</v>
       </c>
       <c r="G6" t="n">
-        <v>31.51944355164684</v>
+        <v>31.79511956069545</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35815656487287</v>
+        <v>34.35939411804895</v>
       </c>
       <c r="I6" t="n">
-        <v>3.828956083918585</v>
+        <v>3.837128280669959</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668227794140335</v>
+        <v>4.668395939952303</v>
       </c>
       <c r="K6" t="n">
-        <v>15.28798466020537</v>
+        <v>14.91150959942677</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79086932126676</v>
+        <v>42.80058087910523</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87256013857284</v>
+        <v>99.87228769999221</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.30719567426591</v>
+        <v>83.60403969678332</v>
       </c>
       <c r="C7" t="n">
-        <v>40.98365468743393</v>
+        <v>41.27205584153852</v>
       </c>
       <c r="D7" t="n">
-        <v>2.00047304953858</v>
+        <v>2.014095419520844</v>
       </c>
       <c r="E7" t="n">
-        <v>7.806437768957184</v>
+        <v>7.866443208789244</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478712686253897</v>
+        <v>0.7478968450326016</v>
       </c>
       <c r="G7" t="n">
-        <v>30.48126410591878</v>
+        <v>30.69630533287975</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40207835676793</v>
+        <v>34.40325487149967</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19487569554936</v>
+        <v>3.201688737607459</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674195428908686</v>
+        <v>4.67435528145376</v>
       </c>
       <c r="K7" t="n">
-        <v>16.69280432573409</v>
+        <v>16.39596030321665</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21718109561203</v>
+        <v>42.22539695855955</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89364010878005</v>
+        <v>99.89341310331473</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.08829564498079</v>
+        <v>88.4139615015914</v>
       </c>
       <c r="C8" t="n">
-        <v>43.21489273355474</v>
+        <v>43.55163262691993</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004728923219508</v>
+        <v>2.018355299093888</v>
       </c>
       <c r="E8" t="n">
-        <v>9.591036715827588</v>
+        <v>9.682479687225316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494623151279148</v>
+        <v>0.7494786720215415</v>
       </c>
       <c r="G8" t="n">
-        <v>30.96160159634972</v>
+        <v>31.19343213680449</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47526649588409</v>
+        <v>34.47601891299091</v>
       </c>
       <c r="I8" t="n">
-        <v>5.622060129022503</v>
+        <v>5.609955093320635</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684139469549468</v>
+        <v>4.684241700134635</v>
       </c>
       <c r="K8" t="n">
-        <v>11.91170435501922</v>
+        <v>11.58603849840859</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68639874607928</v>
+        <v>44.67572504493862</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81299583465324</v>
+        <v>99.81339617026714</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.18995856293544</v>
+        <v>86.44683386246903</v>
       </c>
       <c r="C9" t="n">
-        <v>42.18933415306585</v>
+        <v>42.45577858565074</v>
       </c>
       <c r="D9" t="n">
-        <v>1.918781550935049</v>
+        <v>1.929271459671639</v>
       </c>
       <c r="E9" t="n">
-        <v>9.962105823700039</v>
+        <v>10.03569306871265</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508227373879154</v>
+        <v>0.7508321483100691</v>
       </c>
       <c r="G9" t="n">
-        <v>29.63420602276215</v>
+        <v>29.81665238908047</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53784591984412</v>
+        <v>34.53827882226317</v>
       </c>
       <c r="I9" t="n">
-        <v>4.69355439963169</v>
+        <v>4.683405047493111</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692642108674471</v>
+        <v>4.692700926937932</v>
       </c>
       <c r="K9" t="n">
-        <v>13.81004143706456</v>
+        <v>13.55316613753095</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84445607295231</v>
+        <v>43.83522319089274</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84383166308272</v>
+        <v>99.84416791407443</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.11962335866693</v>
+        <v>84.32380492342587</v>
       </c>
       <c r="C10" t="n">
-        <v>40.84746348602104</v>
+        <v>41.05989304999454</v>
       </c>
       <c r="D10" t="n">
-        <v>1.825922942338899</v>
+        <v>1.834069928316741</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13288846621553</v>
+        <v>10.1919513313236</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519882395519426</v>
+        <v>0.7519923204427046</v>
       </c>
       <c r="G10" t="n">
-        <v>28.20007135704975</v>
+        <v>28.34532446729581</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59145901938937</v>
+        <v>34.5916467403644</v>
       </c>
       <c r="I10" t="n">
-        <v>3.91736683692179</v>
+        <v>3.908868132915682</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699926497199642</v>
+        <v>4.699952002766904</v>
       </c>
       <c r="K10" t="n">
-        <v>15.88037664133308</v>
+        <v>15.67619507657416</v>
       </c>
       <c r="L10" t="n">
-        <v>43.141783361545</v>
+        <v>43.13381728877869</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86962348889911</v>
+        <v>99.86990541534739</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.95978436287268</v>
+        <v>81.93756066405871</v>
       </c>
       <c r="C11" t="n">
-        <v>39.29511073671213</v>
+        <v>39.27999213980556</v>
       </c>
       <c r="D11" t="n">
-        <v>1.730017416210806</v>
+        <v>1.72795266865972</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14546651907144</v>
+        <v>10.14587501689419</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529879609022671</v>
+        <v>0.7529901463629892</v>
       </c>
       <c r="G11" t="n">
-        <v>26.71887923352932</v>
+        <v>26.70529531130875</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6374462015043</v>
+        <v>34.63754673269749</v>
       </c>
       <c r="I11" t="n">
-        <v>3.268812276015382</v>
+        <v>3.261712373366873</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70617475563917</v>
+        <v>4.706188414768683</v>
       </c>
       <c r="K11" t="n">
-        <v>18.04021563712732</v>
+        <v>18.06243933594131</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5558578806905</v>
+        <v>42.54898885389438</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89118425452995</v>
+        <v>99.89142032964124</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.65691693116931</v>
+        <v>79.42231228448469</v>
       </c>
       <c r="C12" t="n">
-        <v>37.49848540301259</v>
+        <v>37.2698803710637</v>
       </c>
       <c r="D12" t="n">
-        <v>1.628646368836908</v>
+        <v>1.617139896722338</v>
       </c>
       <c r="E12" t="n">
-        <v>10.00550874779333</v>
+        <v>9.948757928643911</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538472659249228</v>
+        <v>0.7538501209989298</v>
       </c>
       <c r="G12" t="n">
-        <v>25.15327605105274</v>
+        <v>24.99269759232849</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67697423254646</v>
+        <v>34.67710556595076</v>
       </c>
       <c r="I12" t="n">
-        <v>2.727118852984174</v>
+        <v>2.721197923596959</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711545412030768</v>
+        <v>4.711563256243311</v>
       </c>
       <c r="K12" t="n">
-        <v>20.34308306883069</v>
+        <v>20.57768771551532</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06763118715628</v>
+        <v>42.06182879193857</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90919965899957</v>
+        <v>99.90939687851758</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.38206898359797</v>
+        <v>76.88926913436718</v>
       </c>
       <c r="C13" t="n">
-        <v>35.64519699339549</v>
+        <v>35.15734654463132</v>
       </c>
       <c r="D13" t="n">
-        <v>1.529431959885888</v>
+        <v>1.506573874909797</v>
       </c>
       <c r="E13" t="n">
-        <v>9.775127578007881</v>
+        <v>9.646864090694924</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545859690786743</v>
+        <v>0.7545919504403742</v>
       </c>
       <c r="G13" t="n">
-        <v>23.6209806035338</v>
+        <v>23.28391336608533</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71095457761903</v>
+        <v>34.71122972025721</v>
       </c>
       <c r="I13" t="n">
-        <v>2.274825988730997</v>
+        <v>2.269896441727219</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716162306741714</v>
+        <v>4.716199690252338</v>
       </c>
       <c r="K13" t="n">
-        <v>22.61793101640202</v>
+        <v>23.1107308656328</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6611186887307</v>
+        <v>41.65633375852487</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92424669852821</v>
+        <v>99.92441116878899</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.98445517631052</v>
+        <v>83.56404135692088</v>
       </c>
       <c r="C14" t="n">
-        <v>39.58400387548502</v>
+        <v>39.3276246040619</v>
       </c>
       <c r="D14" t="n">
-        <v>1.531365007416155</v>
+        <v>1.508309910262382</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00725796116347</v>
+        <v>11.968932222994</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555396895331694</v>
+        <v>0.7554614718920315</v>
       </c>
       <c r="G14" t="n">
-        <v>25.33987140043136</v>
+        <v>25.14023848900333</v>
       </c>
       <c r="H14" t="n">
-        <v>36.44386198157306</v>
+        <v>36.58072261775725</v>
       </c>
       <c r="I14" t="n">
-        <v>3.184436076610983</v>
+        <v>2.888742445686698</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72212305958231</v>
+        <v>4.721634199325196</v>
       </c>
       <c r="K14" t="n">
-        <v>16.01554482368949</v>
+        <v>16.4359586430791</v>
       </c>
       <c r="L14" t="n">
-        <v>44.2944374224404</v>
+        <v>44.14023616754728</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89398612161492</v>
+        <v>99.90381941468829</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.33560830109676</v>
+        <v>82.62562799633955</v>
       </c>
       <c r="C15" t="n">
-        <v>39.42746997174859</v>
+        <v>38.83574296213799</v>
       </c>
       <c r="D15" t="n">
-        <v>1.507407949490263</v>
+        <v>1.473088251167675</v>
       </c>
       <c r="E15" t="n">
-        <v>12.26216615687674</v>
+        <v>12.09104109492064</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563425090738964</v>
+        <v>0.7561958603526455</v>
       </c>
       <c r="G15" t="n">
-        <v>24.94344810223997</v>
+        <v>24.55317020575822</v>
       </c>
       <c r="H15" t="n">
-        <v>36.48258641252445</v>
+        <v>36.61628294951596</v>
       </c>
       <c r="I15" t="n">
-        <v>2.656516489179584</v>
+        <v>2.409625507420378</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727140681711854</v>
+        <v>4.726224127204034</v>
       </c>
       <c r="K15" t="n">
-        <v>16.66439169890325</v>
+        <v>17.37437200366046</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81968177166452</v>
+        <v>43.70964218848802</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91154344231634</v>
+        <v>99.91975715428646</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.97339569747739</v>
+        <v>80.14658741591479</v>
       </c>
       <c r="C16" t="n">
-        <v>37.47611273755866</v>
+        <v>36.72912504113838</v>
       </c>
       <c r="D16" t="n">
-        <v>1.416719172279056</v>
+        <v>1.37843398020095</v>
       </c>
       <c r="E16" t="n">
-        <v>11.89374607071733</v>
+        <v>11.64907310256396</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570324026985896</v>
+        <v>0.7568279215972722</v>
       </c>
       <c r="G16" t="n">
-        <v>23.4427987202407</v>
+        <v>22.97548982991805</v>
       </c>
       <c r="H16" t="n">
-        <v>36.51586380137456</v>
+        <v>36.64688842435137</v>
       </c>
       <c r="I16" t="n">
-        <v>2.215783013300963</v>
+        <v>2.009699647300241</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731452516866185</v>
+        <v>4.730174509982951</v>
       </c>
       <c r="K16" t="n">
-        <v>19.02660430252263</v>
+        <v>19.85341258408521</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42349083521929</v>
+        <v>43.35052833290364</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92620787530058</v>
+        <v>99.93306595812722</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.58738892325913</v>
+        <v>81.66747168942577</v>
       </c>
       <c r="C17" t="n">
-        <v>38.63950612656949</v>
+        <v>37.84785835183906</v>
       </c>
       <c r="D17" t="n">
-        <v>1.418005977772673</v>
+        <v>1.379559270801358</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65720210261209</v>
+        <v>12.36971773655258</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577200149464507</v>
+        <v>0.7574457613767124</v>
       </c>
       <c r="G17" t="n">
-        <v>23.84167428018246</v>
+        <v>23.37203284758436</v>
       </c>
       <c r="H17" t="n">
-        <v>36.92661362143364</v>
+        <v>37.05459214797366</v>
       </c>
       <c r="I17" t="n">
-        <v>2.250422832896492</v>
+        <v>2.000087916532639</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735750093415317</v>
+        <v>4.734036008604452</v>
       </c>
       <c r="K17" t="n">
-        <v>17.41261107674087</v>
+        <v>18.33252831057422</v>
       </c>
       <c r="L17" t="n">
-        <v>43.87293677570258</v>
+        <v>43.75299812199118</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92505397901293</v>
+        <v>99.93338478440447</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.32244788217652</v>
+        <v>79.3164411921578</v>
       </c>
       <c r="C18" t="n">
-        <v>36.72222006122226</v>
+        <v>35.80551510745432</v>
       </c>
       <c r="D18" t="n">
-        <v>1.334340749479072</v>
+        <v>1.293092415255171</v>
       </c>
       <c r="E18" t="n">
-        <v>12.22320367893907</v>
+        <v>11.87240367874966</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583101773974451</v>
+        <v>0.7579766937630089</v>
       </c>
       <c r="G18" t="n">
-        <v>22.43496714860441</v>
+        <v>21.9071402323661</v>
       </c>
       <c r="H18" t="n">
-        <v>36.95537450985136</v>
+        <v>37.08056560249087</v>
       </c>
       <c r="I18" t="n">
-        <v>1.876813009171119</v>
+        <v>1.667908233514171</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739438608734032</v>
+        <v>4.737354336018806</v>
       </c>
       <c r="K18" t="n">
-        <v>19.67755211782348</v>
+        <v>20.68355880784223</v>
       </c>
       <c r="L18" t="n">
-        <v>43.53771607559604</v>
+        <v>43.45536808702198</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93748825464178</v>
+        <v>99.94444200231852</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.42463960664281</v>
+        <v>78.34387282894569</v>
       </c>
       <c r="C19" t="n">
-        <v>36.11368195238228</v>
+        <v>35.08350184127558</v>
       </c>
       <c r="D19" t="n">
-        <v>1.301911107530087</v>
+        <v>1.2577164863072</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18697223211666</v>
+        <v>11.78039464522413</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588082530323458</v>
+        <v>0.758427145454758</v>
       </c>
       <c r="G19" t="n">
-        <v>21.88971065992224</v>
+        <v>21.30781304803605</v>
       </c>
       <c r="H19" t="n">
-        <v>36.97964765317796</v>
+        <v>37.10260190472034</v>
       </c>
       <c r="I19" t="n">
-        <v>1.565038119411366</v>
+        <v>1.396749940110972</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742551581452161</v>
+        <v>4.740169659092238</v>
       </c>
       <c r="K19" t="n">
-        <v>20.57536039335719</v>
+        <v>21.65612717105433</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25882395956133</v>
+        <v>43.21384030866493</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94786630530079</v>
+        <v>99.95346932099483</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.98146226985421</v>
+        <v>75.74004229783411</v>
       </c>
       <c r="C20" t="n">
-        <v>33.91159132128652</v>
+        <v>32.69451384114821</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21268847654414</v>
+        <v>1.162962321237241</v>
       </c>
       <c r="E20" t="n">
-        <v>11.56926332601162</v>
+        <v>11.08697274527476</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592370124126555</v>
+        <v>0.7588158566195575</v>
       </c>
       <c r="G20" t="n">
-        <v>20.38956401757228</v>
+        <v>19.70251960009733</v>
       </c>
       <c r="H20" t="n">
-        <v>37.00054274854426</v>
+        <v>37.1216178322091</v>
       </c>
       <c r="I20" t="n">
-        <v>1.30493536119016</v>
+        <v>1.164554838523871</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745231327579097</v>
+        <v>4.742599103872235</v>
       </c>
       <c r="K20" t="n">
-        <v>23.01853773014579</v>
+        <v>24.25995770216589</v>
       </c>
       <c r="L20" t="n">
-        <v>43.02639766747292</v>
+        <v>43.00672984723839</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95652671890524</v>
+        <v>99.96120139055249</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.54176710744279</v>
+        <v>81.59112117046649</v>
       </c>
       <c r="C21" t="n">
-        <v>37.22002846303297</v>
+        <v>36.37035272979463</v>
       </c>
       <c r="D21" t="n">
-        <v>1.213684898026539</v>
+        <v>1.163726517949744</v>
       </c>
       <c r="E21" t="n">
-        <v>13.39431234664789</v>
+        <v>13.05903774706505</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598608495184194</v>
+        <v>0.7593144837654545</v>
       </c>
       <c r="G21" t="n">
-        <v>21.88275269616772</v>
+        <v>21.41217338298222</v>
       </c>
       <c r="H21" t="n">
-        <v>38.50738005691674</v>
+        <v>38.84271791680185</v>
       </c>
       <c r="I21" t="n">
-        <v>2.034645950675358</v>
+        <v>1.60843559836808</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749130309490121</v>
+        <v>4.745715523534091</v>
       </c>
       <c r="K21" t="n">
-        <v>17.45823289255722</v>
+        <v>18.40887882953349</v>
       </c>
       <c r="L21" t="n">
-        <v>45.25397279342594</v>
+        <v>45.16718912834529</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93223414901613</v>
+        <v>99.94642068767341</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_92_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.41956405321881</v>
+        <v>45.34964941435702</v>
       </c>
       <c r="M2" t="n">
-        <v>99.380181828204</v>
+        <v>100.1458791910312</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0551754084282</v>
+        <v>88.07170803976773</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9169200996526</v>
+        <v>45.94584620492746</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228810999069803</v>
+        <v>2.228831446599456</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701245838243782</v>
+        <v>5.71858807438609</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429369996899342</v>
+        <v>0.7429438155331519</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9687297302944</v>
+        <v>33.97861452271654</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17510198573697</v>
+        <v>34.17541551452499</v>
       </c>
       <c r="I3" t="n">
-        <v>6.594993607331213</v>
+        <v>6.583915818925304</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643356248062089</v>
+        <v>4.643398847082199</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94482459157181</v>
+        <v>11.92829196023229</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90153739558928</v>
+        <v>48.88954371113573</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632820868137</v>
+        <v>106.7636818762955</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.26130107438176</v>
+        <v>87.18546263516185</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76382056760305</v>
+        <v>42.6971652072579</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191180870402089</v>
+        <v>2.1863038714508</v>
       </c>
       <c r="E4" t="n">
-        <v>6.522887206790818</v>
+        <v>6.525828604626486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444999849680809</v>
+        <v>0.7445055443666186</v>
       </c>
       <c r="G4" t="n">
-        <v>33.39521870986096</v>
+        <v>33.33028012992667</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24699930853172</v>
+        <v>34.24725504086445</v>
       </c>
       <c r="I4" t="n">
-        <v>5.507390087777588</v>
+        <v>5.498129791635465</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653124906050506</v>
+        <v>4.653159652291366</v>
       </c>
       <c r="K4" t="n">
-        <v>12.73869892561823</v>
+        <v>12.81453736483815</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31428623990841</v>
+        <v>44.30541087737826</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8168057331297</v>
+        <v>99.81711344947431</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.29079101357235</v>
+        <v>86.1691501550314</v>
       </c>
       <c r="C5" t="n">
-        <v>42.64819200118164</v>
+        <v>42.53423480796728</v>
       </c>
       <c r="D5" t="n">
-        <v>2.144481727997771</v>
+        <v>2.137241280590566</v>
       </c>
       <c r="E5" t="n">
-        <v>7.150143163686387</v>
+        <v>7.144368237826932</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458222369162092</v>
+        <v>0.7458274456926102</v>
       </c>
       <c r="G5" t="n">
-        <v>32.68348920582009</v>
+        <v>32.58231919063306</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30782289814562</v>
+        <v>34.30806250186006</v>
       </c>
       <c r="I5" t="n">
-        <v>4.597642800279955</v>
+        <v>4.589909962849368</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661388980726308</v>
+        <v>4.661421535578813</v>
       </c>
       <c r="K5" t="n">
-        <v>13.70920898642766</v>
+        <v>13.83084984496859</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48961595439688</v>
+        <v>43.48218951951871</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84701694200618</v>
+        <v>99.84727417245458</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.08849040057324</v>
+        <v>84.79243788221518</v>
       </c>
       <c r="C6" t="n">
-        <v>42.16019722146022</v>
+        <v>41.87053137676718</v>
       </c>
       <c r="D6" t="n">
-        <v>2.086192588191413</v>
+        <v>2.070069879054492</v>
       </c>
       <c r="E6" t="n">
-        <v>7.595316562622791</v>
+        <v>7.558275228471259</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469433503923684</v>
+        <v>0.7469505922224142</v>
       </c>
       <c r="G6" t="n">
-        <v>31.79511956069545</v>
+        <v>31.5582887897577</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35939411804895</v>
+        <v>34.35972724223105</v>
       </c>
       <c r="I6" t="n">
-        <v>3.837128280669959</v>
+        <v>3.830684949088201</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668395939952303</v>
+        <v>4.668441201390088</v>
       </c>
       <c r="K6" t="n">
-        <v>14.91150959942677</v>
+        <v>15.20756211778478</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80058087910523</v>
+        <v>42.79440900648001</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87228769999221</v>
+        <v>99.87250250103197</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.60403969678332</v>
+        <v>83.39322933393292</v>
       </c>
       <c r="C7" t="n">
-        <v>41.27205584153852</v>
+        <v>41.06641551748581</v>
       </c>
       <c r="D7" t="n">
-        <v>2.014095419520844</v>
+        <v>2.002299539722333</v>
       </c>
       <c r="E7" t="n">
-        <v>7.866443208789244</v>
+        <v>7.843550298428147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478968450326016</v>
+        <v>0.7479049023276761</v>
       </c>
       <c r="G7" t="n">
-        <v>30.69630533287975</v>
+        <v>30.52512756091985</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40325487149967</v>
+        <v>34.40362550707309</v>
       </c>
       <c r="I7" t="n">
-        <v>3.201688737607459</v>
+        <v>3.196315885913846</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67435528145376</v>
+        <v>4.674405639547975</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39596030321665</v>
+        <v>16.6067706660671</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22539695855955</v>
+        <v>42.22040590119463</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89341310331473</v>
+        <v>99.89359208474752</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.4139615015914</v>
+        <v>88.33780676167949</v>
       </c>
       <c r="C8" t="n">
-        <v>43.55163262691993</v>
+        <v>43.39363364979255</v>
       </c>
       <c r="D8" t="n">
-        <v>2.018355299093888</v>
+        <v>2.006597917873409</v>
       </c>
       <c r="E8" t="n">
-        <v>9.682479687225316</v>
+        <v>9.696205632315055</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494786720215415</v>
+        <v>0.7495104453683014</v>
       </c>
       <c r="G8" t="n">
-        <v>31.19343213680449</v>
+        <v>31.03447367194182</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47601891299091</v>
+        <v>34.47748048694186</v>
       </c>
       <c r="I8" t="n">
-        <v>5.609955093320635</v>
+        <v>5.689098323687168</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684241700134635</v>
+        <v>4.684440283551883</v>
       </c>
       <c r="K8" t="n">
-        <v>11.58603849840859</v>
+        <v>11.66219323832051</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67572504493862</v>
+        <v>44.75494272591065</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81339617026714</v>
+        <v>99.8107696140237</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.44683386246903</v>
+        <v>86.45970726916124</v>
       </c>
       <c r="C9" t="n">
-        <v>42.45577858565074</v>
+        <v>42.39884071993686</v>
       </c>
       <c r="D9" t="n">
-        <v>1.929271459671639</v>
+        <v>1.921930402428905</v>
       </c>
       <c r="E9" t="n">
-        <v>10.03569306871265</v>
+        <v>10.07867793124763</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508321483100691</v>
+        <v>0.7508829044168669</v>
       </c>
       <c r="G9" t="n">
-        <v>29.81665238908047</v>
+        <v>29.72498772285046</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53827882226317</v>
+        <v>34.54061360317587</v>
       </c>
       <c r="I9" t="n">
-        <v>4.683405047493111</v>
+        <v>4.749596552436093</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692700926937932</v>
+        <v>4.693018152605418</v>
       </c>
       <c r="K9" t="n">
-        <v>13.55316613753095</v>
+        <v>13.54029273083878</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83522319089274</v>
+        <v>43.90283604023304</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84416791407443</v>
+        <v>99.84196949100867</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.32380492342587</v>
+        <v>84.35999175249708</v>
       </c>
       <c r="C10" t="n">
-        <v>41.05989304999454</v>
+        <v>41.03642963211806</v>
       </c>
       <c r="D10" t="n">
-        <v>1.834069928316741</v>
+        <v>1.828073999682528</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1919513313236</v>
+        <v>10.24719077397779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519923204427046</v>
+        <v>0.7520590731943576</v>
       </c>
       <c r="G10" t="n">
-        <v>28.34532446729581</v>
+        <v>28.27338447237835</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5916467403644</v>
+        <v>34.59471736694044</v>
       </c>
       <c r="I10" t="n">
-        <v>3.908868132915682</v>
+        <v>3.964196858858871</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699952002766904</v>
+        <v>4.700369207464735</v>
       </c>
       <c r="K10" t="n">
-        <v>15.67619507657416</v>
+        <v>15.64000824750292</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13381728877869</v>
+        <v>43.19162888281137</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86990541534739</v>
+        <v>99.86806676243235</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.93756066405871</v>
+        <v>82.20455750635014</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27999213980556</v>
+        <v>39.49585697014984</v>
       </c>
       <c r="D11" t="n">
-        <v>1.72795266865972</v>
+        <v>1.732738939736353</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14587501689419</v>
+        <v>10.26411558089609</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529901463629892</v>
+        <v>0.7530678403133173</v>
       </c>
       <c r="G11" t="n">
-        <v>26.70529531130875</v>
+        <v>26.7989119925862</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63754673269749</v>
+        <v>34.64112065441259</v>
       </c>
       <c r="I11" t="n">
-        <v>3.261712373366873</v>
+        <v>3.307928496447359</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706188414768683</v>
+        <v>4.706674001958232</v>
       </c>
       <c r="K11" t="n">
-        <v>18.06243933594131</v>
+        <v>17.79544249364985</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54898885389438</v>
+        <v>42.59858395678757</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89142032964124</v>
+        <v>99.88988342058727</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.42231228448469</v>
+        <v>80.01075887581148</v>
       </c>
       <c r="C12" t="n">
-        <v>37.2698803710637</v>
+        <v>37.81447023638876</v>
       </c>
       <c r="D12" t="n">
-        <v>1.617139896722338</v>
+        <v>1.636636672459453</v>
       </c>
       <c r="E12" t="n">
-        <v>9.948757928643911</v>
+        <v>10.1548034346161</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538501209989298</v>
+        <v>0.7539336817553348</v>
       </c>
       <c r="G12" t="n">
-        <v>24.99269759232849</v>
+        <v>25.31257371970506</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67710556595076</v>
+        <v>34.68094936074539</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721197923596959</v>
+        <v>2.759776495559288</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711563256243311</v>
+        <v>4.712085510970842</v>
       </c>
       <c r="K12" t="n">
-        <v>20.57768771551532</v>
+        <v>19.98924112418852</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06182879193857</v>
+        <v>42.10440173674363</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90939687851758</v>
+        <v>99.90811309732091</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.88926913436718</v>
+        <v>77.78365874478398</v>
       </c>
       <c r="C13" t="n">
-        <v>35.15734654463132</v>
+        <v>36.01414966855832</v>
       </c>
       <c r="D13" t="n">
-        <v>1.506573874909797</v>
+        <v>1.539918250563192</v>
       </c>
       <c r="E13" t="n">
-        <v>9.646864090694924</v>
+        <v>9.93837720834482</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545919504403742</v>
+        <v>0.754677461630735</v>
       </c>
       <c r="G13" t="n">
-        <v>23.28391336608533</v>
+        <v>23.81670586735904</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71122972025721</v>
+        <v>34.7151632350138</v>
       </c>
       <c r="I13" t="n">
-        <v>2.269896441727219</v>
+        <v>2.302082586680279</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716199690252338</v>
+        <v>4.716734135192093</v>
       </c>
       <c r="K13" t="n">
-        <v>23.1107308656328</v>
+        <v>22.21634125521604</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65633375852487</v>
+        <v>41.69284861801565</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92441116878899</v>
+        <v>99.92333954179</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.56404135692088</v>
+        <v>84.28052083148022</v>
       </c>
       <c r="C14" t="n">
-        <v>39.3276246040619</v>
+        <v>39.91057641142537</v>
       </c>
       <c r="D14" t="n">
-        <v>1.508309910262382</v>
+        <v>1.541848838325155</v>
       </c>
       <c r="E14" t="n">
-        <v>11.968932222994</v>
+        <v>12.14786106974776</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554614718920315</v>
+        <v>0.7556235969668937</v>
       </c>
       <c r="G14" t="n">
-        <v>25.14023848900333</v>
+        <v>25.51527859520515</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58072261775725</v>
+        <v>36.42739930402142</v>
       </c>
       <c r="I14" t="n">
-        <v>2.888742445686698</v>
+        <v>3.169861946170759</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721634199325196</v>
+        <v>4.722647481043085</v>
       </c>
       <c r="K14" t="n">
-        <v>16.4359586430791</v>
+        <v>15.71947916851978</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14023616754728</v>
+        <v>44.26441465731503</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90381941468829</v>
+        <v>99.89447023726018</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.62562799633955</v>
+        <v>83.71474944699985</v>
       </c>
       <c r="C15" t="n">
-        <v>38.83574296213799</v>
+        <v>39.83509931939939</v>
       </c>
       <c r="D15" t="n">
-        <v>1.473088251167675</v>
+        <v>1.521198259016717</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09104109492064</v>
+        <v>12.42588221446612</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561958603526455</v>
+        <v>0.7564192036301225</v>
       </c>
       <c r="G15" t="n">
-        <v>24.55317020575822</v>
+        <v>25.17354257601178</v>
       </c>
       <c r="H15" t="n">
-        <v>36.61628294951596</v>
+        <v>36.46575422269616</v>
       </c>
       <c r="I15" t="n">
-        <v>2.409625507420378</v>
+        <v>2.644332948490676</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726224127204034</v>
+        <v>4.727620022688265</v>
       </c>
       <c r="K15" t="n">
-        <v>17.37437200366046</v>
+        <v>16.28525055300017</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70964218848802</v>
+        <v>43.79159840687347</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91975715428646</v>
+        <v>99.91194827927302</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.14658741591479</v>
+        <v>81.51303295807072</v>
       </c>
       <c r="C16" t="n">
-        <v>36.72912504113838</v>
+        <v>38.04259422926378</v>
       </c>
       <c r="D16" t="n">
-        <v>1.37843398020095</v>
+        <v>1.436879729626479</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64907310256396</v>
+        <v>12.10472745477584</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568279215972722</v>
+        <v>0.757101449099395</v>
       </c>
       <c r="G16" t="n">
-        <v>22.97548982991805</v>
+        <v>23.77819777005342</v>
       </c>
       <c r="H16" t="n">
-        <v>36.64688842435137</v>
+        <v>36.4986441803845</v>
       </c>
       <c r="I16" t="n">
-        <v>2.009699647300241</v>
+        <v>2.205598317259857</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730174509982951</v>
+        <v>4.731884056871218</v>
       </c>
       <c r="K16" t="n">
-        <v>19.85341258408521</v>
+        <v>18.48696704192929</v>
       </c>
       <c r="L16" t="n">
-        <v>43.35052833290364</v>
+        <v>43.39698503579331</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93306595812722</v>
+        <v>99.92654630698638</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.66747168942577</v>
+        <v>83.20443699033234</v>
       </c>
       <c r="C17" t="n">
-        <v>37.84785835183906</v>
+        <v>39.2594021507835</v>
       </c>
       <c r="D17" t="n">
-        <v>1.379559270801358</v>
+        <v>1.438167448397832</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36971773655258</v>
+        <v>12.8937710299522</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574457613767124</v>
+        <v>0.7577799566513652</v>
       </c>
       <c r="G17" t="n">
-        <v>23.37203284758436</v>
+        <v>24.20486764110258</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05459214797366</v>
+        <v>36.93671400181561</v>
       </c>
       <c r="I17" t="n">
-        <v>2.000087916532639</v>
+        <v>2.237012183341704</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734036008604452</v>
+        <v>4.736124729071031</v>
       </c>
       <c r="K17" t="n">
-        <v>18.33252831057422</v>
+        <v>16.79556300966767</v>
       </c>
       <c r="L17" t="n">
-        <v>43.75299812199118</v>
+        <v>43.87053453327939</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93338478440447</v>
+        <v>99.92549969373056</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.3164411921578</v>
+        <v>81.05707987178737</v>
       </c>
       <c r="C18" t="n">
-        <v>35.80551510745432</v>
+        <v>37.45792509413425</v>
       </c>
       <c r="D18" t="n">
-        <v>1.293092415255171</v>
+        <v>1.359071416936965</v>
       </c>
       <c r="E18" t="n">
-        <v>11.87240367874966</v>
+        <v>12.49557661950411</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579766937630089</v>
+        <v>0.758361324581343</v>
       </c>
       <c r="G18" t="n">
-        <v>21.9071402323661</v>
+        <v>22.87365341109091</v>
       </c>
       <c r="H18" t="n">
-        <v>37.08056560249087</v>
+        <v>36.9650518072312</v>
       </c>
       <c r="I18" t="n">
-        <v>1.667908233514171</v>
+        <v>1.865607013809458</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737354336018806</v>
+        <v>4.739758278633393</v>
       </c>
       <c r="K18" t="n">
-        <v>20.68355880784223</v>
+        <v>18.94292012821263</v>
       </c>
       <c r="L18" t="n">
-        <v>43.45536808702198</v>
+        <v>43.53701555033806</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94444200231852</v>
+        <v>99.93786077268494</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.34387282894569</v>
+        <v>80.211137327469</v>
       </c>
       <c r="C19" t="n">
-        <v>35.08350184127558</v>
+        <v>36.89983231304629</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2577164863072</v>
+        <v>1.328627073552127</v>
       </c>
       <c r="E19" t="n">
-        <v>11.78039464522413</v>
+        <v>12.47494478765984</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758427145454758</v>
+        <v>0.7588515996901205</v>
       </c>
       <c r="G19" t="n">
-        <v>21.30781304803605</v>
+        <v>22.3612643267244</v>
       </c>
       <c r="H19" t="n">
-        <v>37.10260190472034</v>
+        <v>36.98894944574244</v>
       </c>
       <c r="I19" t="n">
-        <v>1.396749940110972</v>
+        <v>1.555677596036835</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740169659092238</v>
+        <v>4.742822498063252</v>
       </c>
       <c r="K19" t="n">
-        <v>21.65612717105433</v>
+        <v>19.78886267253098</v>
       </c>
       <c r="L19" t="n">
-        <v>43.21384030866493</v>
+        <v>43.25948259737248</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95346932099483</v>
+        <v>99.94817758294975</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.74004229783411</v>
+        <v>77.84663725169877</v>
       </c>
       <c r="C20" t="n">
-        <v>32.69451384114821</v>
+        <v>34.77525404463911</v>
       </c>
       <c r="D20" t="n">
-        <v>1.162962321237241</v>
+        <v>1.242449545883715</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08697274527476</v>
+        <v>11.88198014640256</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588158566195575</v>
+        <v>0.7592730780104135</v>
       </c>
       <c r="G20" t="n">
-        <v>19.70251960009733</v>
+        <v>20.91086600685202</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1216178322091</v>
+        <v>37.00949370009753</v>
       </c>
       <c r="I20" t="n">
-        <v>1.164554838523871</v>
+        <v>1.297118036887437</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742599103872235</v>
+        <v>4.745456737565084</v>
       </c>
       <c r="K20" t="n">
-        <v>24.25995770216589</v>
+        <v>22.15336274830125</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00672984723839</v>
+        <v>43.02816994050306</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96120139055249</v>
+        <v>99.95678673344341</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.59112117046649</v>
+        <v>83.23808148415685</v>
       </c>
       <c r="C21" t="n">
-        <v>36.37035272979463</v>
+        <v>37.99816992241813</v>
       </c>
       <c r="D21" t="n">
-        <v>1.163726517949744</v>
+        <v>1.243436607070936</v>
       </c>
       <c r="E21" t="n">
-        <v>13.05903774706505</v>
+        <v>13.65981363414329</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593144837654545</v>
+        <v>0.7598762807628218</v>
       </c>
       <c r="G21" t="n">
-        <v>21.41217338298222</v>
+        <v>22.36523095923578</v>
       </c>
       <c r="H21" t="n">
-        <v>38.84271791680185</v>
+        <v>38.47664817026587</v>
       </c>
       <c r="I21" t="n">
-        <v>1.60843559836808</v>
+        <v>1.983849077910524</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745715523534091</v>
+        <v>4.749226754767635</v>
       </c>
       <c r="K21" t="n">
-        <v>18.40887882953349</v>
+        <v>16.76191851584313</v>
       </c>
       <c r="L21" t="n">
-        <v>45.16718912834529</v>
+        <v>45.17383575291625</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94642068767341</v>
+        <v>99.93392419117752</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_92_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.34964941435702</v>
+        <v>43.23727680976735</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1458791910312</v>
+        <v>95.88456876366328</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07170803976773</v>
+        <v>81.50991650407374</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94584620492746</v>
+        <v>43.26547205962931</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228831446599456</v>
+        <v>2.181053288755356</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71858807438609</v>
+        <v>4.168422400516523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429438155331519</v>
+        <v>0.7376562716361115</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97861452271654</v>
+        <v>32.80667655169515</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17541551452499</v>
+        <v>33.93218849526112</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583915818925304</v>
+        <v>3.073567798483798</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643398847082199</v>
+        <v>4.610351697725696</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92829196023229</v>
+        <v>18.49008349592625</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88954371113573</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636818762955</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.18546263516185</v>
+        <v>88.72995238237468</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6971652072579</v>
+        <v>42.90523361052657</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1863038714508</v>
+        <v>2.186842867444932</v>
       </c>
       <c r="E4" t="n">
-        <v>6.525828604626486</v>
+        <v>6.584987600106912</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445055443666186</v>
+        <v>0.7396143709877021</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33028012992667</v>
+        <v>33.50768017824631</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24725504086445</v>
+        <v>34.02226106543429</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498129791635465</v>
+        <v>7.065976481481381</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653159652291366</v>
+        <v>4.622589818673138</v>
       </c>
       <c r="K4" t="n">
-        <v>12.81453736483815</v>
+        <v>11.27004761762533</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30541087737826</v>
+        <v>45.58980978543322</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81711344947431</v>
+        <v>99.76509101358512</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.1691501550314</v>
+        <v>87.80314735324869</v>
       </c>
       <c r="C5" t="n">
-        <v>42.53423480796728</v>
+        <v>43.07370561008783</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137241280590566</v>
+        <v>2.143697367407063</v>
       </c>
       <c r="E5" t="n">
-        <v>7.144368237826932</v>
+        <v>7.438652883079735</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458274456926102</v>
+        <v>0.741271425755058</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58231919063306</v>
+        <v>32.84658758768055</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30806250186006</v>
+        <v>34.09848558473266</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589909962849368</v>
+        <v>5.901506093624501</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661421535578813</v>
+        <v>4.632946410969112</v>
       </c>
       <c r="K5" t="n">
-        <v>13.83084984496859</v>
+        <v>12.19685264675132</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48218951951871</v>
+        <v>44.53316461867524</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727417245458</v>
+        <v>99.8037228755144</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.79243788221518</v>
+        <v>86.62605445643169</v>
       </c>
       <c r="C6" t="n">
-        <v>41.87053137676718</v>
+        <v>42.81276999121992</v>
       </c>
       <c r="D6" t="n">
-        <v>2.070069879054492</v>
+        <v>2.088177090694623</v>
       </c>
       <c r="E6" t="n">
-        <v>7.558275228471259</v>
+        <v>8.06720460026108</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469505922224142</v>
+        <v>0.7426768638459814</v>
       </c>
       <c r="G6" t="n">
-        <v>31.5582887897577</v>
+        <v>31.99588372450733</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35972724223105</v>
+        <v>34.16313573691514</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830684949088201</v>
+        <v>4.927246041170148</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668441201390088</v>
+        <v>4.641730399037383</v>
       </c>
       <c r="K6" t="n">
-        <v>15.20756211778478</v>
+        <v>13.37394554356832</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79440900648001</v>
+        <v>43.64935374038886</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87250250103197</v>
+        <v>99.8360692751771</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.39322933393292</v>
+        <v>85.23507627630256</v>
       </c>
       <c r="C7" t="n">
-        <v>41.06641551748581</v>
+        <v>42.1873038271202</v>
       </c>
       <c r="D7" t="n">
-        <v>2.002299539722333</v>
+        <v>2.022515614691396</v>
       </c>
       <c r="E7" t="n">
-        <v>7.843550298428147</v>
+        <v>8.498976578487882</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479049023276761</v>
+        <v>0.7438713502938671</v>
       </c>
       <c r="G7" t="n">
-        <v>30.52512756091985</v>
+        <v>30.98979235383727</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40362550707309</v>
+        <v>34.21808211351787</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196315885913846</v>
+        <v>4.112642326137612</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674405639547975</v>
+        <v>4.649195939336668</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6067706660671</v>
+        <v>14.76492372369744</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22040590119463</v>
+        <v>42.91090450359431</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89359208474752</v>
+        <v>99.86313205441193</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.33780676167949</v>
+        <v>83.56228287430115</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39363364979255</v>
+        <v>41.15356281838368</v>
       </c>
       <c r="D8" t="n">
-        <v>2.006597917873409</v>
+        <v>1.943670901949255</v>
       </c>
       <c r="E8" t="n">
-        <v>9.696205632315055</v>
+        <v>8.739639123154133</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495104453683014</v>
+        <v>0.7448897074447539</v>
       </c>
       <c r="G8" t="n">
-        <v>31.03447367194182</v>
+        <v>29.78170216242992</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47748048694186</v>
+        <v>34.26492654245867</v>
       </c>
       <c r="I8" t="n">
-        <v>5.689098323687168</v>
+        <v>3.431893765334706</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684440283551883</v>
+        <v>4.65556067152971</v>
       </c>
       <c r="K8" t="n">
-        <v>11.66219323832051</v>
+        <v>16.43771712569885</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75494272591065</v>
+        <v>42.29447999130255</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8107696140237</v>
+        <v>99.88575993538508</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.45970726916124</v>
+        <v>81.60773254738976</v>
       </c>
       <c r="C9" t="n">
-        <v>42.39884071993686</v>
+        <v>39.73200347991873</v>
       </c>
       <c r="D9" t="n">
-        <v>1.921930402428905</v>
+        <v>1.851950626087295</v>
       </c>
       <c r="E9" t="n">
-        <v>10.07867793124763</v>
+        <v>8.804431906219538</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508829044168669</v>
+        <v>0.7457608708352123</v>
       </c>
       <c r="G9" t="n">
-        <v>29.72498772285046</v>
+        <v>28.37632744840947</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54061360317587</v>
+        <v>34.30500005841975</v>
       </c>
       <c r="I9" t="n">
-        <v>4.749596552436093</v>
+        <v>2.863256194698424</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693018152605418</v>
+        <v>4.661005442720075</v>
       </c>
       <c r="K9" t="n">
-        <v>13.54029273083878</v>
+        <v>18.39226745261023</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90283604023304</v>
+        <v>41.78039868510064</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84196949100867</v>
+        <v>99.90466961762959</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.35999175249708</v>
+        <v>86.10927136756595</v>
       </c>
       <c r="C10" t="n">
-        <v>41.03642963211806</v>
+        <v>42.91283196549175</v>
       </c>
       <c r="D10" t="n">
-        <v>1.828073999682528</v>
+        <v>1.853962582980071</v>
       </c>
       <c r="E10" t="n">
-        <v>10.24719077397779</v>
+        <v>10.61675268773946</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520590731943576</v>
+        <v>0.7465710645322275</v>
       </c>
       <c r="G10" t="n">
-        <v>28.27338447237835</v>
+        <v>29.74216607834768</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59471736694044</v>
+        <v>35.67727959102281</v>
       </c>
       <c r="I10" t="n">
-        <v>3.964196858858871</v>
+        <v>2.806470209617284</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700369207464735</v>
+        <v>4.66606915332642</v>
       </c>
       <c r="K10" t="n">
-        <v>15.64000824750292</v>
+        <v>13.89072863243404</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19162888281137</v>
+        <v>43.10299191632107</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86806676243235</v>
+        <v>99.90655251424685</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.20455750635014</v>
+        <v>85.71659192082132</v>
       </c>
       <c r="C11" t="n">
-        <v>39.49585697014984</v>
+        <v>42.822385855352</v>
       </c>
       <c r="D11" t="n">
-        <v>1.732738939736353</v>
+        <v>1.827509914108969</v>
       </c>
       <c r="E11" t="n">
-        <v>10.26411558089609</v>
+        <v>10.91952942249092</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530678403133173</v>
+        <v>0.7472742107228701</v>
       </c>
       <c r="G11" t="n">
-        <v>26.7989119925862</v>
+        <v>29.36840389723606</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64112065441259</v>
+        <v>35.76148602484623</v>
       </c>
       <c r="I11" t="n">
-        <v>3.307928496447359</v>
+        <v>2.421924634398338</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706674001958232</v>
+        <v>4.670463817017937</v>
       </c>
       <c r="K11" t="n">
-        <v>17.79544249364985</v>
+        <v>14.28340807917867</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59858395678757</v>
+        <v>42.81355120782921</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88988342058727</v>
+        <v>99.91934514235987</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.01075887581148</v>
+        <v>83.73703511988623</v>
       </c>
       <c r="C12" t="n">
-        <v>37.81447023638876</v>
+        <v>41.21953906506793</v>
       </c>
       <c r="D12" t="n">
-        <v>1.636636672459453</v>
+        <v>1.743011628676402</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1548034346161</v>
+        <v>10.75129376673459</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539336817553348</v>
+        <v>0.7478750656101903</v>
       </c>
       <c r="G12" t="n">
-        <v>25.31257371970506</v>
+        <v>28.01050167408041</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68094936074539</v>
+        <v>35.79024048117235</v>
       </c>
       <c r="I12" t="n">
-        <v>2.759776495559288</v>
+        <v>2.019893343548603</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712085510970842</v>
+        <v>4.674219160063688</v>
       </c>
       <c r="K12" t="n">
-        <v>19.98924112418852</v>
+        <v>16.26296488011377</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10440173674363</v>
+        <v>42.45022037052945</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90811309732091</v>
+        <v>99.93272431571116</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.78365874478398</v>
+        <v>84.77219971672112</v>
       </c>
       <c r="C13" t="n">
-        <v>36.01414966855832</v>
+        <v>42.12381775244339</v>
       </c>
       <c r="D13" t="n">
-        <v>1.539918250563192</v>
+        <v>1.744273880085095</v>
       </c>
       <c r="E13" t="n">
-        <v>9.93837720834482</v>
+        <v>11.34843835345156</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754677461630735</v>
+        <v>0.7484166605941603</v>
       </c>
       <c r="G13" t="n">
-        <v>23.81670586735904</v>
+        <v>28.31319401813065</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7151632350138</v>
+        <v>36.09856674418616</v>
       </c>
       <c r="I13" t="n">
-        <v>2.302082586680279</v>
+        <v>1.841705931559995</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716734135192093</v>
+        <v>4.677604128713501</v>
       </c>
       <c r="K13" t="n">
-        <v>22.21634125521604</v>
+        <v>15.2278002832789</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69284861801565</v>
+        <v>42.58703619184365</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92333954179</v>
+        <v>99.93865422756593</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.28052083148022</v>
+        <v>82.71393620233653</v>
       </c>
       <c r="C14" t="n">
-        <v>39.91057641142537</v>
+        <v>40.35185188837134</v>
       </c>
       <c r="D14" t="n">
-        <v>1.541848838325155</v>
+        <v>1.658592878394788</v>
       </c>
       <c r="E14" t="n">
-        <v>12.14786106974776</v>
+        <v>11.04693909695463</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556235969668937</v>
+        <v>0.7488798421296896</v>
       </c>
       <c r="G14" t="n">
-        <v>25.51527859520515</v>
+        <v>26.92241310223052</v>
       </c>
       <c r="H14" t="n">
-        <v>36.42739930402142</v>
+        <v>36.12090749427275</v>
       </c>
       <c r="I14" t="n">
-        <v>3.169861946170759</v>
+        <v>1.535704775043597</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722647481043085</v>
+        <v>4.680499013310559</v>
       </c>
       <c r="K14" t="n">
-        <v>15.71947916851978</v>
+        <v>17.28606379766346</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26441465731503</v>
+        <v>42.31092581586633</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89447023726018</v>
+        <v>99.94884150190113</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.71474944699985</v>
+        <v>81.74536355228074</v>
       </c>
       <c r="C15" t="n">
-        <v>39.83509931939939</v>
+        <v>39.58759358224655</v>
       </c>
       <c r="D15" t="n">
-        <v>1.521198259016717</v>
+        <v>1.617269570540019</v>
       </c>
       <c r="E15" t="n">
-        <v>12.42588221446612</v>
+        <v>10.99059362146915</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564192036301225</v>
+        <v>0.7492808897234378</v>
       </c>
       <c r="G15" t="n">
-        <v>25.17354257601178</v>
+        <v>26.25164984301921</v>
       </c>
       <c r="H15" t="n">
-        <v>36.46575422269616</v>
+        <v>36.14025132250744</v>
       </c>
       <c r="I15" t="n">
-        <v>2.644332948490676</v>
+        <v>1.313312744249989</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727620022688265</v>
+        <v>4.683005560771485</v>
       </c>
       <c r="K15" t="n">
-        <v>16.28525055300017</v>
+        <v>18.25463644771928</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79159840687347</v>
+        <v>42.1140163099551</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91194827927302</v>
+        <v>99.95624633992092</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.51303295807072</v>
+        <v>79.28868718455871</v>
       </c>
       <c r="C16" t="n">
-        <v>38.04259422926378</v>
+        <v>37.33452210484231</v>
       </c>
       <c r="D16" t="n">
-        <v>1.436879729626479</v>
+        <v>1.515724094008073</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10472745477584</v>
+        <v>10.4830023296551</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757101449099395</v>
+        <v>0.7496257942965681</v>
       </c>
       <c r="G16" t="n">
-        <v>23.77819777005342</v>
+        <v>24.60335549455815</v>
       </c>
       <c r="H16" t="n">
-        <v>36.4986441803845</v>
+        <v>36.15688719047921</v>
       </c>
       <c r="I16" t="n">
-        <v>2.205598317259857</v>
+        <v>1.094931067208079</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731884056871218</v>
+        <v>4.685161214353549</v>
       </c>
       <c r="K16" t="n">
-        <v>18.48696704192929</v>
+        <v>20.71131281544128</v>
       </c>
       <c r="L16" t="n">
-        <v>43.39698503579331</v>
+        <v>41.91768417015391</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92654630698638</v>
+        <v>99.9635190904375</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.20443699033234</v>
+        <v>84.09451891143362</v>
       </c>
       <c r="C17" t="n">
-        <v>39.2594021507835</v>
+        <v>40.56247480388014</v>
       </c>
       <c r="D17" t="n">
-        <v>1.438167448397832</v>
+        <v>1.51641033815632</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8937710299522</v>
+        <v>12.18904338512208</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577799566513652</v>
+        <v>0.7499651874069267</v>
       </c>
       <c r="G17" t="n">
-        <v>24.20486764110258</v>
+        <v>26.12542055539332</v>
       </c>
       <c r="H17" t="n">
-        <v>36.93671400181561</v>
+        <v>37.68418311328276</v>
       </c>
       <c r="I17" t="n">
-        <v>2.237012183341704</v>
+        <v>1.142213910778928</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736124729071031</v>
+        <v>4.687282421293291</v>
       </c>
       <c r="K17" t="n">
-        <v>16.79556300966767</v>
+        <v>15.90548108856638</v>
       </c>
       <c r="L17" t="n">
-        <v>43.87053453327939</v>
+        <v>43.49398754063981</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92549969373056</v>
+        <v>99.96194343308633</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.05707987178737</v>
+        <v>85.69958805058377</v>
       </c>
       <c r="C18" t="n">
-        <v>37.45792509413425</v>
+        <v>41.27363407762374</v>
       </c>
       <c r="D18" t="n">
-        <v>1.359071416936965</v>
+        <v>1.517583927052184</v>
       </c>
       <c r="E18" t="n">
-        <v>12.49557661950411</v>
+        <v>12.77123917349164</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758361324581343</v>
+        <v>0.7505456047214748</v>
       </c>
       <c r="G18" t="n">
-        <v>22.87365341109091</v>
+        <v>26.26620809750787</v>
       </c>
       <c r="H18" t="n">
-        <v>36.9650518072312</v>
+        <v>37.71334787016858</v>
       </c>
       <c r="I18" t="n">
-        <v>1.865607013809458</v>
+        <v>1.989753348132812</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739758278633393</v>
+        <v>4.690910029509216</v>
       </c>
       <c r="K18" t="n">
-        <v>18.94292012821263</v>
+        <v>14.30041194941623</v>
       </c>
       <c r="L18" t="n">
-        <v>43.53701555033806</v>
+        <v>44.35968015236701</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93786077268494</v>
+        <v>99.93372617940697</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.211137327469</v>
+        <v>82.98314124031808</v>
       </c>
       <c r="C19" t="n">
-        <v>36.89983231304629</v>
+        <v>38.86548462419257</v>
       </c>
       <c r="D19" t="n">
-        <v>1.328627073552127</v>
+        <v>1.416877216642482</v>
       </c>
       <c r="E19" t="n">
-        <v>12.47494478765984</v>
+        <v>12.2002799002994</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588515996901205</v>
+        <v>0.7510458388487239</v>
       </c>
       <c r="G19" t="n">
-        <v>22.3612643267244</v>
+        <v>24.52318527993309</v>
       </c>
       <c r="H19" t="n">
-        <v>36.98894944574244</v>
+        <v>37.73848358948903</v>
       </c>
       <c r="I19" t="n">
-        <v>1.555677596036835</v>
+        <v>1.659232922300827</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742822498063252</v>
+        <v>4.694036492804522</v>
       </c>
       <c r="K19" t="n">
-        <v>19.78886267253098</v>
+        <v>17.01685875968194</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25948259737248</v>
+        <v>44.06238568978848</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94817758294975</v>
+        <v>99.94472907366298</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.84663725169877</v>
+        <v>80.1692167004977</v>
       </c>
       <c r="C20" t="n">
-        <v>34.77525404463911</v>
+        <v>36.30791271288953</v>
       </c>
       <c r="D20" t="n">
-        <v>1.242449545883715</v>
+        <v>1.313097521436112</v>
       </c>
       <c r="E20" t="n">
-        <v>11.88198014640256</v>
+        <v>11.53724747137293</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592730780104135</v>
+        <v>0.7514778683562507</v>
       </c>
       <c r="G20" t="n">
-        <v>20.91086600685202</v>
+        <v>22.72697551387333</v>
       </c>
       <c r="H20" t="n">
-        <v>37.00949370009753</v>
+        <v>37.76019216922761</v>
       </c>
       <c r="I20" t="n">
-        <v>1.297118036887437</v>
+        <v>1.383489479004894</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745456737565084</v>
+        <v>4.696736677226565</v>
       </c>
       <c r="K20" t="n">
-        <v>22.15336274830125</v>
+        <v>19.83078329950232</v>
       </c>
       <c r="L20" t="n">
-        <v>43.02816994050306</v>
+        <v>43.81521418421091</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95678673344341</v>
+        <v>99.95391019660275</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.23808148415685</v>
+        <v>77.25103055448629</v>
       </c>
       <c r="C21" t="n">
-        <v>37.99816992241813</v>
+        <v>33.6027635455557</v>
       </c>
       <c r="D21" t="n">
-        <v>1.243436607070936</v>
+        <v>1.20599225326164</v>
       </c>
       <c r="E21" t="n">
-        <v>13.65981363414329</v>
+        <v>10.78843714355574</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598762807628218</v>
+        <v>0.7518518939976669</v>
       </c>
       <c r="G21" t="n">
-        <v>22.36523095923578</v>
+        <v>20.87320702564571</v>
       </c>
       <c r="H21" t="n">
-        <v>38.47664817026587</v>
+        <v>37.778986175932</v>
       </c>
       <c r="I21" t="n">
-        <v>1.983849077910524</v>
+        <v>1.153481724608112</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749226754767635</v>
+        <v>4.699074337485416</v>
       </c>
       <c r="K21" t="n">
-        <v>16.76191851584313</v>
+        <v>22.74896944551371</v>
       </c>
       <c r="L21" t="n">
-        <v>45.17383575291625</v>
+        <v>43.60983674562492</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93392419117752</v>
+        <v>99.96156973669433</v>
       </c>
     </row>
   </sheetData>
